--- a/artfynd/A 36126-2025 artfynd.xlsx
+++ b/artfynd/A 36126-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17279498</v>
+        <v>79468529</v>
       </c>
       <c r="B2" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,19 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kulleråsmyran, Mpd</t>
+          <t>Slättberget, Timrå, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613912.4146511815</v>
+        <v>613894</v>
       </c>
       <c r="R2" t="n">
-        <v>6951691.530630052</v>
+        <v>6951584</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-10-15</t>
+          <t>2019-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-10-15</t>
+          <t>2019-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gran i gles tallskoged genomslag.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,81 +781,67 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Håkan Sundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Håkan Sundin, Eva Sundin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17279522</v>
+        <v>119628857</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kulleråsmyran, Mpd</t>
+          <t>Ã…s, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613912.4146511815</v>
+        <v>613982</v>
       </c>
       <c r="R3" t="n">
-        <v>6951691.530630052</v>
+        <v>6951477</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-10-15</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,27 +892,18 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Hällmarksskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Caroline Westerlund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36126-2025 artfynd.xlsx
+++ b/artfynd/A 36126-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79468529</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,8 +914,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628857</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>